--- a/Cardapio.xlsx
+++ b/Cardapio.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Cardápio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Configuração" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Configuração" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cardápio'!$A$2:$D$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cardápio'!$A$2:$D$70</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cardápio'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cardápio'!$A$1:$D$71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cardápio'!$B$1:$I$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,22 +35,40 @@
     <font>
       <b val="1"/>
       <color rgb="001B291E"/>
-      <sz val="18"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <color rgb="00888888"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
+      <sz val="11.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="00808080"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="6">
@@ -81,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -103,36 +121,53 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A0A0A0"/>
+      </right>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -213,12 +248,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="666750" cy="666750"/>
+    <ext cx="323850" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -226,6 +261,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="323850" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -528,1217 +588,2383 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="68" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col hidden="1" width="3" customWidth="1" min="1" max="1"/>
+    <col width="8.5" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col hidden="1" width="3" customWidth="1" min="6" max="6"/>
+    <col width="8.5" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="14.5" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CARDÁPIO 06/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CARDÁPIO 21/09/2026</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>✂</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CARDÁPIO 21/09/2026</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>IMP</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>CÓD</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>ITENS</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>R$</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>CÓD</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>ITENS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>APERITIVO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>APERITIVO</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Cachaça de Banana</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="9" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Cachaça de Banana</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Cachaça Matuta Black Blend</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="9" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Cachaça Matuta Black Blend</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Cachaça Matuta Cristal</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="9" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Cachaça Matuta Cristal</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Cachaça Matuta Umburana</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="9" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Cachaça Matuta Umburana</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Campari</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="9" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" hidden="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Campari</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" hidden="1" ht="16.5" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>teste fiscal consumer</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="12" t="n">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>teste fiscal consumer</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>BEBIDAS NÃO ALCOÓLICAS</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>BEBIDAS NÃO ALCOÓLICAS</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Água Mineral</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="9" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Água Mineral</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Água Mineral com gás</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="9" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Água Mineral com gás</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Água Tônica Schweppes</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Água Tônica Schweppes</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+    </row>
+    <row r="14" ht="16.5" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Coca Cola Zero Lata</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Coca Cola Zero Lata</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Cola Cola Lata</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Cola Cola Lata</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Fanta Laranja Lata</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Fanta Laranja Lata</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Guarana Antarctica Lata</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Guarana Antarctica Lata</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Red Bull</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="9" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Red Bull Cereja</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="9" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Red Bull Cereja</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>CERVEJAS LONG NECK</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CERVEJAS LONG NECK</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Cerveja Budweiser</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="9" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Cerveja Budweiser</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Cerveja Budweiser Zero - Long Neck</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="9" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Cerveja Budweiser Zero - Long Neck</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Cerveja Heineken</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="9" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" hidden="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Cerveja Heineken</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" hidden="1" ht="18" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>COUVERT ARTISTICO</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n"/>
-    </row>
-    <row r="25" hidden="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>COUVERT ARTISTICO</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+    </row>
+    <row r="25" hidden="1" ht="16.5" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>Couvert 26-02-17</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="12" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" hidden="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Couvert 26-02-17</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" hidden="1" ht="16.5" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Couvert 26-03-20</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="12" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Couvert 26-03-20</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>DESTILADOS</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>DESTILADOS</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Gin Beefeater</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="9" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" hidden="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n">
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Gin Beefeater</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" hidden="1" ht="16.5" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Gin Gordon´s</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="12" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Gin Gordon´s</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Gin Tanqueray</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="9" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Gin Tanqueray</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Rolha Destilados</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="9" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Rolha Destilados</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Vodka Absolut</t>
         </is>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="9" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Vodka Absolut</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Vodka Smirnoff</t>
         </is>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="9" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Vodka Smirnoff</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Whisky Chivas 12 anos</t>
         </is>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="9" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Whisky Chivas 12 anos</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Whisky Old Parr 12 anos</t>
         </is>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="9" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Whisky Old Parr 12 anos</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Whisky Red Label 8 anos</t>
         </is>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="9" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Whisky Red Label 8 anos</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>PETISCOS</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>PETISCOS</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Bolinho de Bacalhau (06 unidades)</t>
         </is>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="9" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="39" hidden="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Bolinho de Bacalhau (06 unidades)</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" hidden="1" ht="16.5" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Caldinho de Camarão</t>
         </is>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="12" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" hidden="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="n">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Caldinho de Camarão</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" hidden="1" ht="16.5" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Caldinho de Feijão</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="12" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Caldinho de Feijão</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Camarão Empanado (08 unidades)</t>
         </is>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D41" s="9" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Camarão Empanado (08 unidades)</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Camarão Frito c/ Arroz e Farofa</t>
         </is>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D42" s="9" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" hidden="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="n">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Camarão Frito c/ Arroz e Farofa</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" hidden="1" ht="16.5" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>Carne de Sol Defumada c/ Macaxeira e Farofa</t>
         </is>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="12" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="44" hidden="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="n">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Carne de Sol Defumada c/ Macaxeira e Farofa</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" hidden="1" ht="16.5" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Casquinho de Carangueijo c/ Farofa</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="12" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Casquinho de Carangueijo c/ Farofa</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>Coxinha com Massa de Macaxeira (08 unidades)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="9" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Coxinha com Massa de Macaxeira (08 unidades)</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Croquete de Macaxeira c/ Carne de Sol</t>
         </is>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D46" s="9" t="n">
         <v>35</v>
       </c>
-    </row>
-    <row r="47" hidden="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="n">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Croquete de Macaxeira c/ Carne de Sol</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" hidden="1" ht="16.5" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>Cubos de Carne de Sol na Manteiga da Terra c/ Macaxeira Frita</t>
         </is>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D47" s="12" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="n">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Cubos de Carne de Sol na Manteiga da Terra c/ Macaxeira Frita</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>Dadinho de Tapioca com Geléia de Pimenta (06 unidades)</t>
         </is>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D48" s="9" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Dadinho de Tapioca com Geléia de Pimenta (06 unidades)</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>Escondidinho de Carne de Sol</t>
         </is>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="D49" s="9" t="n">
         <v>45</v>
       </c>
-    </row>
-    <row r="50" hidden="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="n">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Escondidinho de Carne de Sol</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" ht="16.5" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>Espetinho de Franco c/ vinagrete de feijao verde e farofa</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="12" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="51" hidden="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="n">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Espetinho de Franco c/ vinagrete de feijao verde e farofa</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" ht="16.5" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>Espetinho de Suino c/ vinagrete de feijao verde e farofa</t>
         </is>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D51" s="12" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="52" hidden="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="n">
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>Espetinho de Suino c/ vinagrete de feijao verde e farofa</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" ht="16.5" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>Frango a Passarinho</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="12" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n">
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Frango a Passarinho</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>Kibe (06 unidades)</t>
         </is>
       </c>
-      <c r="D53" s="7" t="n">
+      <c r="D53" s="9" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="54" hidden="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="n">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>Kibe (06 unidades)</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" hidden="1" ht="16.5" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>Lagarto ao Molho Madeira c/ Arroz e Fritas</t>
         </is>
       </c>
-      <c r="D54" s="10" t="n">
+      <c r="D54" s="12" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="n">
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Lagarto ao Molho Madeira c/ Arroz e Fritas</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>Macaxeira Frita c/ Queijo Parmesão</t>
         </is>
       </c>
-      <c r="D55" s="7" t="n">
+      <c r="D55" s="9" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="n">
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Macaxeira Frita c/ Queijo Parmesão</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Pastel de Camarão c/ Queijo (06 unidades)</t>
         </is>
       </c>
-      <c r="D56" s="7" t="n">
+      <c r="D56" s="9" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="n">
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Pastel de Camarão c/ Queijo (06 unidades)</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>Pastel de Carne Moida (06 unidades)</t>
         </is>
       </c>
-      <c r="D57" s="7" t="n">
+      <c r="D57" s="9" t="n">
         <v>35</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="n">
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Pastel de Carne Moida (06 unidades)</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Polenta Frita c/ Queijo Parmesão</t>
         </is>
       </c>
-      <c r="D58" s="7" t="n">
+      <c r="D58" s="9" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="59" hidden="1">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="n">
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Polenta Frita c/ Queijo Parmesão</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" hidden="1" ht="16.5" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>Pratinho de Vatapá de Frango c/ Arroz, Paçoca e Calabresa</t>
         </is>
       </c>
-      <c r="D59" s="10" t="n">
+      <c r="D59" s="12" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="60" hidden="1">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="n">
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>Pratinho de Vatapá de Frango c/ Arroz, Paçoca e Calabresa</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" hidden="1" ht="16.5" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>Risoles de Camarão (06 unidades)</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n">
+      <c r="D60" s="12" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="61" hidden="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="n">
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>Risoles de Camarão (06 unidades)</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" hidden="1" ht="16.5" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>Unha de Carangueijo (05 unidades)</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n">
+      <c r="D61" s="12" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>Unha de Carangueijo (05 unidades)</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>VINHOS &amp; ESPUMANTES</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="n">
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>VINHOS &amp; ESPUMANTES</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="n"/>
+      <c r="I62" s="6" t="n"/>
+    </row>
+    <row r="63" ht="16.5" customHeight="1">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Espumante Brut Espanhol</t>
         </is>
       </c>
-      <c r="D63" s="7" t="n">
+      <c r="D63" s="9" t="n">
         <v>90</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="n">
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Espumante Brut Espanhol</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" customHeight="1">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Rolha Vinho &amp; Espumante</t>
         </is>
       </c>
-      <c r="D64" s="7" t="n">
+      <c r="D64" s="9" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="n">
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Rolha Vinho &amp; Espumante</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" customHeight="1">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Vinho Branco (Diversos)</t>
         </is>
       </c>
-      <c r="D65" s="7" t="n">
+      <c r="D65" s="9" t="n">
         <v>90</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="n">
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Vinho Branco (Diversos)</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" customHeight="1">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Vinho Rose (Diversos)</t>
         </is>
       </c>
-      <c r="D66" s="7" t="n">
+      <c r="D66" s="9" t="n">
         <v>90</v>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="n">
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Vinho Rose (Diversos)</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" customHeight="1">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>Vinho Tinto (Diversos)</t>
         </is>
       </c>
-      <c r="D67" s="7" t="n">
+      <c r="D67" s="9" t="n">
         <v>90</v>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Vinho Tinto (Diversos)</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>Cobramos 10% como taxa de serviço</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="C68" s="13" t="n"/>
+      <c r="D68" s="13" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>Cobramos 10% como taxa de serviço</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="n"/>
+      <c r="I68" s="13" t="n"/>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>Rede WI-FI: Clientes Le Clair    Senha: @Clientes2026</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
+      <c r="C69" s="13" t="n"/>
+      <c r="D69" s="13" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>Rede WI-FI: Clientes Le Clair    Senha: @Clientes2026</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="n"/>
+      <c r="I69" s="13" t="n"/>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>PIX (CNPJ) 64.111.665/0001-55</t>
         </is>
       </c>
+      <c r="C70" s="13" t="n"/>
+      <c r="D70" s="13" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>PIX (CPF) 428.255.047-34</t>
+        </is>
+      </c>
+      <c r="H70" s="13" t="n"/>
+      <c r="I70" s="13" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D71"/>
-  <mergeCells count="4">
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A71:D71"/>
+  <autoFilter ref="A2:D70"/>
+  <mergeCells count="22">
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B70:D70"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.2" header="0.05" footer="0.05"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1749,7 +2975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1757,12 +2983,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Configuração</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -1776,7 +3002,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\TIC01\Desktop\RM-Projeto-LeClair\Produtos (58).xlsx</t>
+          <t>C:\Users\TIC01.CETREDE\Desktop\Gerador-de-Cardapios\Produtos (58).xlsx</t>
         </is>
       </c>
     </row>
@@ -1788,47 +3014,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C:\Users\TIC01\Desktop\RM-Projeto-LeClair\cardapio 2026-07-28.xlsx</t>
+          <t>C:\Users\TIC01.CETREDE\Desktop\Gerador-de-Cardapios\cardapio 2026-07-28.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Produtos incluídos</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>58</v>
+          <t>Layout de impressão</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2 Vias (Paisagem)</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Produtos ativos</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42</v>
+          <t>Itens em negrito</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Produtos pausados</t>
+          <t>Produtos incluídos</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Produtos ativos</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Produtos pausados</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Pausados ocultos</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
